--- a/artfynd/A 1817-2024 artfynd.xlsx
+++ b/artfynd/A 1817-2024 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 1817-2024 artfynd.xlsx
+++ b/artfynd/A 1817-2024 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>114529777</v>
       </c>
       <c r="B7" t="n">
-        <v>57527</v>
+        <v>57532</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>

--- a/artfynd/A 1817-2024 artfynd.xlsx
+++ b/artfynd/A 1817-2024 artfynd.xlsx
@@ -1230,11 +1230,6 @@
       <c r="E7" t="n">
         <v>103021</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Poecile montanus</t>

--- a/artfynd/A 1817-2024 artfynd.xlsx
+++ b/artfynd/A 1817-2024 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>114529777</v>
       </c>
       <c r="B7" t="n">
-        <v>57532</v>
+        <v>57536</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1229,6 +1229,11 @@
       </c>
       <c r="E7" t="n">
         <v>103021</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>

--- a/artfynd/A 1817-2024 artfynd.xlsx
+++ b/artfynd/A 1817-2024 artfynd.xlsx
@@ -1215,7 +1215,7 @@
         <v>114529777</v>
       </c>
       <c r="B7" t="n">
-        <v>57536</v>
+        <v>57537</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
